--- a/Loss_Reserve_Table.xlsx
+++ b/Loss_Reserve_Table.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Ng Jing Jia\Python Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440705E5-BCC9-47F5-B998-3C71440FAE3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95657398-89EC-4B25-8D46-C8C9C9764806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>fnol_month</t>
   </si>
@@ -43,13 +43,16 @@
   <si>
     <t>1 to 2</t>
   </si>
+  <si>
+    <t>April 2023 IBNR</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -86,10 +89,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -392,7 +396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.109375" bestFit="1" customWidth="1"/>
@@ -956,6 +960,15 @@
         <v>1.049514777572758</v>
       </c>
     </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" s="2">
+        <f>D38-C38</f>
+        <v>63060.920003159204</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
